--- a/paper/results.xlsx
+++ b/paper/results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jaitej\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/71600677250d0614/Documents/MTech/Thesis/Yolov26_experiments_raspberryPi/ronin_yolov26/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9091D59E-E410-46CB-80C3-50A39B8B3F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9091D59E-E410-46CB-80C3-50A39B8B3F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94620AFA-51E9-459A-8831-8436E2121F7B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1B44670D-8AB3-4C03-85DD-5F85B107A258}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{1B44670D-8AB3-4C03-85DD-5F85B107A258}"/>
   </bookViews>
   <sheets>
     <sheet name="Tinycnn_random" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="lignttcn" sheetId="9" r:id="rId5"/>
     <sheet name="shufflenet" sheetId="8" r:id="rId6"/>
     <sheet name="All results " sheetId="5" r:id="rId7"/>
+    <sheet name="yolo26_eff_rf_random_benchmark_" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="37">
   <si>
     <t>model</t>
   </si>
@@ -134,18 +135,6 @@
     <t>measured energy J/run</t>
   </si>
   <si>
-    <t>tinyCNN old</t>
-  </si>
-  <si>
-    <t>tinyCNN new</t>
-  </si>
-  <si>
-    <t>eff YOLOv26 old</t>
-  </si>
-  <si>
-    <t>eff YOLOv26 new</t>
-  </si>
-  <si>
     <t>tinyCNN random</t>
   </si>
   <si>
@@ -162,6 +151,9 @@
   </si>
   <si>
     <t>lighttcn</t>
+  </si>
+  <si>
+    <t>yolo26_eff_A_rf</t>
   </si>
 </sst>
 </file>
@@ -382,20 +374,8 @@
               <c:f>'All results '!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>tinyCNN old</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>tinyCNN new</c:v>
-                </c:pt>
                 <c:pt idx="2">
                   <c:v>tinyCNN random</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>eff YOLOv26 old</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>eff YOLOv26 new</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>eff YOLOv26 random</c:v>
@@ -409,20 +389,8 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>3.53</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.0209999999999999</c:v>
-                </c:pt>
                 <c:pt idx="2">
                   <c:v>4.34</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.6280000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>3.54</c:v>
@@ -750,20 +718,8 @@
               <c:f>'All results '!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>tinyCNN old</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>tinyCNN new</c:v>
-                </c:pt>
                 <c:pt idx="2">
                   <c:v>tinyCNN random</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>eff YOLOv26 old</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>eff YOLOv26 new</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>eff YOLOv26 random</c:v>
@@ -777,20 +733,8 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10.79</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10.85</c:v>
-                </c:pt>
                 <c:pt idx="2">
                   <c:v>11.09</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>25.37</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>25.79</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>25.31</c:v>
@@ -1118,20 +1062,8 @@
               <c:f>'All results '!$A$2:$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>tinyCNN old</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>tinyCNN new</c:v>
-                </c:pt>
                 <c:pt idx="2">
                   <c:v>tinyCNN random</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>eff YOLOv26 old</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>eff YOLOv26 new</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>eff YOLOv26 random</c:v>
@@ -1145,20 +1077,8 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>214.17</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>244.1</c:v>
-                </c:pt>
                 <c:pt idx="2">
                   <c:v>359.75</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>458.7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>525.18100000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>671.78</c:v>
@@ -8501,7 +8421,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -8548,7 +8468,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -8595,7 +8515,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -8642,7 +8562,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -8689,7 +8609,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -8736,7 +8656,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -8783,7 +8703,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -8830,7 +8750,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -8877,7 +8797,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -8924,7 +8844,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -8971,7 +8891,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -9018,7 +8938,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -9065,7 +8985,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -9112,7 +9032,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -9159,7 +9079,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -9206,7 +9126,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -9253,7 +9173,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -9300,7 +9220,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -9347,7 +9267,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -9394,7 +9314,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -9441,7 +9361,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -9488,7 +9408,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -9535,7 +9455,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -9582,7 +9502,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -9629,7 +9549,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -9676,7 +9596,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -9723,7 +9643,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -9770,7 +9690,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -9815,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q29">
         <v>80.082999999999998</v>
@@ -9829,7 +9749,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>29</v>
@@ -9876,7 +9796,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -9923,7 +9843,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B32">
         <v>31</v>
@@ -9970,7 +9890,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B33">
         <v>32</v>
@@ -10017,7 +9937,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B34">
         <v>33</v>
@@ -10064,7 +9984,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B35">
         <v>34</v>
@@ -10111,7 +10031,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B36">
         <v>35</v>
@@ -10158,7 +10078,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B37">
         <v>36</v>
@@ -10205,7 +10125,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B38">
         <v>37</v>
@@ -10252,7 +10172,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B39">
         <v>38</v>
@@ -10299,7 +10219,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B40">
         <v>39</v>
@@ -10346,7 +10266,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B41">
         <v>40</v>
@@ -10393,7 +10313,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B42">
         <v>41</v>
@@ -10440,7 +10360,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>42</v>
@@ -10487,7 +10407,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B44">
         <v>43</v>
@@ -10534,7 +10454,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B45">
         <v>44</v>
@@ -10581,7 +10501,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B46">
         <v>45</v>
@@ -10628,7 +10548,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B47">
         <v>46</v>
@@ -10675,7 +10595,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B48">
         <v>47</v>
@@ -10722,7 +10642,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B49">
         <v>48</v>
@@ -10769,7 +10689,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B50">
         <v>49</v>
@@ -10816,7 +10736,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -10939,7 +10859,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10986,7 +10906,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -11033,7 +10953,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -11080,7 +11000,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -11127,7 +11047,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -11174,7 +11094,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -11221,7 +11141,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -11268,7 +11188,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -11315,7 +11235,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -11362,7 +11282,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -11409,7 +11329,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -11456,7 +11376,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -11503,7 +11423,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -11550,7 +11470,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -11597,7 +11517,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -11644,7 +11564,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -11691,7 +11611,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -11738,7 +11658,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -11785,7 +11705,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -11832,7 +11752,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -11879,7 +11799,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -11926,7 +11846,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -11973,7 +11893,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -12020,7 +11940,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -12067,7 +11987,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -12114,7 +12034,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -12161,7 +12081,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -12208,7 +12128,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -12255,7 +12175,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B30">
         <v>29</v>
@@ -12300,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Q30">
         <v>89.415000000000006</v>
@@ -12314,7 +12234,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -12361,7 +12281,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B32">
         <v>31</v>
@@ -12408,7 +12328,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B33">
         <v>32</v>
@@ -12455,7 +12375,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B34">
         <v>33</v>
@@ -12502,7 +12422,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B35">
         <v>34</v>
@@ -12549,7 +12469,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B36">
         <v>35</v>
@@ -12596,7 +12516,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B37">
         <v>36</v>
@@ -12643,7 +12563,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B38">
         <v>37</v>
@@ -12690,7 +12610,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B39">
         <v>38</v>
@@ -12737,7 +12657,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B40">
         <v>39</v>
@@ -12784,7 +12704,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B41">
         <v>40</v>
@@ -12831,7 +12751,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B42">
         <v>41</v>
@@ -12878,7 +12798,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B43">
         <v>42</v>
@@ -12925,7 +12845,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B44">
         <v>43</v>
@@ -12972,7 +12892,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B45">
         <v>44</v>
@@ -13019,7 +12939,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B46">
         <v>45</v>
@@ -13066,7 +12986,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B47">
         <v>46</v>
@@ -13113,7 +13033,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B48">
         <v>47</v>
@@ -13160,7 +13080,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B49">
         <v>48</v>
@@ -13207,7 +13127,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B50">
         <v>49</v>
@@ -13254,7 +13174,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -13377,7 +13297,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -13424,7 +13344,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -13471,7 +13391,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -13518,7 +13438,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -13565,7 +13485,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -13612,7 +13532,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -13659,7 +13579,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -13706,7 +13626,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -13753,7 +13673,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -13800,7 +13720,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -13847,7 +13767,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -13894,7 +13814,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -13941,7 +13861,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -13988,7 +13908,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -14035,7 +13955,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -14082,7 +14002,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -14129,7 +14049,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -14176,7 +14096,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -14223,7 +14143,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -14270,7 +14190,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -14317,7 +14237,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -14364,7 +14284,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -14411,7 +14331,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -14458,7 +14378,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -14505,7 +14425,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -14552,7 +14472,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -14599,7 +14519,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -14646,7 +14566,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -14693,7 +14613,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B30">
         <v>29</v>
@@ -14740,7 +14660,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -14787,7 +14707,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B32">
         <v>31</v>
@@ -14834,7 +14754,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>32</v>
@@ -14881,7 +14801,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B34">
         <v>33</v>
@@ -14928,7 +14848,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B35">
         <v>34</v>
@@ -14975,7 +14895,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B36">
         <v>35</v>
@@ -15022,7 +14942,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B37">
         <v>36</v>
@@ -15069,7 +14989,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B38">
         <v>37</v>
@@ -15116,7 +15036,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B39">
         <v>38</v>
@@ -15163,7 +15083,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B40">
         <v>39</v>
@@ -15210,7 +15130,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B41">
         <v>40</v>
@@ -15257,7 +15177,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B42">
         <v>41</v>
@@ -15304,7 +15224,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B43">
         <v>42</v>
@@ -15351,7 +15271,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B44">
         <v>43</v>
@@ -15398,7 +15318,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B45">
         <v>44</v>
@@ -15445,7 +15365,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B46">
         <v>45</v>
@@ -15492,7 +15412,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B47">
         <v>46</v>
@@ -15539,7 +15459,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B48">
         <v>47</v>
@@ -15586,7 +15506,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B49">
         <v>48</v>
@@ -15633,7 +15553,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B50">
         <v>49</v>
@@ -15680,7 +15600,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -15802,7 +15722,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -15849,7 +15769,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -15896,7 +15816,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -15943,7 +15863,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -15990,7 +15910,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -16037,7 +15957,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -16084,7 +16004,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -16131,7 +16051,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -16178,7 +16098,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -16225,7 +16145,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -16272,7 +16192,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -16319,7 +16239,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -16366,7 +16286,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -16413,7 +16333,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -16460,7 +16380,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -16507,7 +16427,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -16554,7 +16474,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -16601,7 +16521,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -16648,7 +16568,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -16695,7 +16615,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -16742,7 +16662,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -16789,7 +16709,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -16836,7 +16756,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -16883,7 +16803,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -16930,7 +16850,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -16977,7 +16897,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -17024,7 +16944,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -17071,7 +16991,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -17118,7 +17038,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>29</v>
@@ -17165,7 +17085,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -17212,7 +17132,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>31</v>
@@ -17259,7 +17179,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B33">
         <v>32</v>
@@ -17306,7 +17226,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B34">
         <v>33</v>
@@ -17353,7 +17273,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B35">
         <v>34</v>
@@ -17400,7 +17320,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B36">
         <v>35</v>
@@ -17447,7 +17367,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B37">
         <v>36</v>
@@ -17494,7 +17414,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B38">
         <v>37</v>
@@ -17539,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Q38">
         <v>33.359000000000002</v>
@@ -17553,7 +17473,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B39">
         <v>38</v>
@@ -17600,7 +17520,7 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B40">
         <v>39</v>
@@ -17647,7 +17567,7 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B41">
         <v>40</v>
@@ -17694,7 +17614,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B42">
         <v>41</v>
@@ -17741,7 +17661,7 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B43">
         <v>42</v>
@@ -17788,7 +17708,7 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B44">
         <v>43</v>
@@ -17835,7 +17755,7 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B45">
         <v>44</v>
@@ -17882,7 +17802,7 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B46">
         <v>45</v>
@@ -17929,7 +17849,7 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B47">
         <v>46</v>
@@ -17976,7 +17896,7 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B48">
         <v>47</v>
@@ -18023,7 +17943,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B49">
         <v>48</v>
@@ -18070,7 +17990,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B50">
         <v>49</v>
@@ -18117,7 +18037,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B51">
         <v>50</v>
@@ -18211,37 +18131,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2">
-        <v>10.79</v>
-      </c>
-      <c r="C2">
-        <v>3.53</v>
-      </c>
-      <c r="D2">
-        <v>214.17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3">
-        <v>10.85</v>
-      </c>
-      <c r="C3">
-        <v>4.0209999999999999</v>
-      </c>
-      <c r="D3">
-        <v>244.1</v>
-      </c>
-    </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>11.09</v>
@@ -18253,37 +18145,9 @@
         <v>359.75</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5">
-        <v>25.37</v>
-      </c>
-      <c r="C5">
-        <v>3.2</v>
-      </c>
-      <c r="D5">
-        <v>458.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6">
-        <v>25.79</v>
-      </c>
-      <c r="C6">
-        <v>3.6280000000000001</v>
-      </c>
-      <c r="D6">
-        <v>525.18100000000004</v>
-      </c>
-    </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>25.31</v>
@@ -18297,7 +18161,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>80.082999999999998</v>
@@ -18311,7 +18175,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>89.415000000000006</v>
@@ -18325,7 +18189,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B10">
         <v>33.359000000000002</v>
@@ -18339,7 +18203,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>50.11</v>
@@ -18356,4 +18220,2425 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A91D41D0-F462-400F-AF8F-85171BF8B626}">
+  <dimension ref="A1:O52"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>27.065407839999999</v>
+      </c>
+      <c r="E2">
+        <v>223614.3996</v>
+      </c>
+      <c r="F2">
+        <v>221243.95559999999</v>
+      </c>
+      <c r="G2">
+        <v>2370.4439579999998</v>
+      </c>
+      <c r="H2">
+        <v>223614.3996</v>
+      </c>
+      <c r="I2">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="J2">
+        <v>970.2</v>
+      </c>
+      <c r="K2">
+        <v>4.6248149999999999</v>
+      </c>
+      <c r="L2">
+        <v>1116.037523</v>
+      </c>
+      <c r="M2">
+        <v>2.9066314999999999E-2</v>
+      </c>
+      <c r="N2">
+        <v>4.6810307000000002E-2</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>26.88650994</v>
+      </c>
+      <c r="E3">
+        <v>239047.95989999999</v>
+      </c>
+      <c r="F3">
+        <v>236868.2083</v>
+      </c>
+      <c r="G3">
+        <v>2179.7515090000002</v>
+      </c>
+      <c r="H3">
+        <v>239047.95989999999</v>
+      </c>
+      <c r="I3">
+        <v>4.7779999999999996</v>
+      </c>
+      <c r="J3">
+        <v>960.45</v>
+      </c>
+      <c r="K3">
+        <v>4.5885058000000001</v>
+      </c>
+      <c r="L3">
+        <v>1157.4578289999999</v>
+      </c>
+      <c r="M3">
+        <v>2.0769076000000001E-2</v>
+      </c>
+      <c r="N3">
+        <v>1.7173126E-2</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>26.933512159999999</v>
+      </c>
+      <c r="E4">
+        <v>241701.33809999999</v>
+      </c>
+      <c r="F4">
+        <v>239543.90609999999</v>
+      </c>
+      <c r="G4">
+        <v>2157.4320299999999</v>
+      </c>
+      <c r="H4">
+        <v>241701.33809999999</v>
+      </c>
+      <c r="I4">
+        <v>4.758</v>
+      </c>
+      <c r="J4">
+        <v>1019</v>
+      </c>
+      <c r="K4">
+        <v>4.8482010000000004</v>
+      </c>
+      <c r="L4">
+        <v>1206.5435890000001</v>
+      </c>
+      <c r="M4">
+        <v>5.057817E-3</v>
+      </c>
+      <c r="N4">
+        <v>7.1550570000000003E-3</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>27.070708799999998</v>
+      </c>
+      <c r="E5">
+        <v>232131.32800000001</v>
+      </c>
+      <c r="F5">
+        <v>229859.81649999999</v>
+      </c>
+      <c r="G5">
+        <v>2271.5114570000001</v>
+      </c>
+      <c r="H5">
+        <v>232131.32800000001</v>
+      </c>
+      <c r="I5">
+        <v>4.7560000000000002</v>
+      </c>
+      <c r="J5">
+        <v>1000.55</v>
+      </c>
+      <c r="K5">
+        <v>4.7563659999999999</v>
+      </c>
+      <c r="L5">
+        <v>1139.6062879999999</v>
+      </c>
+      <c r="M5">
+        <v>1.5132280999999999E-2</v>
+      </c>
+      <c r="N5">
+        <v>2.5868919000000001E-2</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>27.016506840000002</v>
+      </c>
+      <c r="E6">
+        <v>212511.84280000001</v>
+      </c>
+      <c r="F6">
+        <v>210464.79139999999</v>
+      </c>
+      <c r="G6">
+        <v>2047.0514579999999</v>
+      </c>
+      <c r="H6">
+        <v>212511.84280000001</v>
+      </c>
+      <c r="I6">
+        <v>4.766</v>
+      </c>
+      <c r="J6">
+        <v>973.5</v>
+      </c>
+      <c r="K6">
+        <v>4.6374078000000001</v>
+      </c>
+      <c r="L6">
+        <v>1020.4731839999999</v>
+      </c>
+      <c r="M6">
+        <v>1.0055427E-2</v>
+      </c>
+      <c r="N6">
+        <v>1.1283712E-2</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>27.10475447</v>
+      </c>
+      <c r="E7">
+        <v>158996.48970000001</v>
+      </c>
+      <c r="F7">
+        <v>157322.82130000001</v>
+      </c>
+      <c r="G7">
+        <v>1673.6683849999999</v>
+      </c>
+      <c r="H7">
+        <v>158996.48970000001</v>
+      </c>
+      <c r="I7">
+        <v>4.7279999999999998</v>
+      </c>
+      <c r="J7">
+        <v>1050.5</v>
+      </c>
+      <c r="K7">
+        <v>4.966742</v>
+      </c>
+      <c r="L7">
+        <v>824.32103040000004</v>
+      </c>
+      <c r="M7">
+        <v>1.5513964E-2</v>
+      </c>
+      <c r="N7">
+        <v>1.5435636000000001E-2</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>27.064436130000001</v>
+      </c>
+      <c r="E8">
+        <v>205364.94130000001</v>
+      </c>
+      <c r="F8">
+        <v>203373.43369999999</v>
+      </c>
+      <c r="G8">
+        <v>1991.507603</v>
+      </c>
+      <c r="H8">
+        <v>205364.94130000001</v>
+      </c>
+      <c r="I8">
+        <v>4.742</v>
+      </c>
+      <c r="J8">
+        <v>1027.3</v>
+      </c>
+      <c r="K8">
+        <v>4.8709040000000003</v>
+      </c>
+      <c r="L8">
+        <v>1033.9427450000001</v>
+      </c>
+      <c r="M8">
+        <v>2.7911729999999999E-2</v>
+      </c>
+      <c r="N8">
+        <v>2.8468778E-2</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>26.88154797</v>
+      </c>
+      <c r="E9">
+        <v>150160.32699999999</v>
+      </c>
+      <c r="F9">
+        <v>148596.6298</v>
+      </c>
+      <c r="G9">
+        <v>1563.697187</v>
+      </c>
+      <c r="H9">
+        <v>150160.32699999999</v>
+      </c>
+      <c r="I9">
+        <v>4.76</v>
+      </c>
+      <c r="J9">
+        <v>992.95</v>
+      </c>
+      <c r="K9">
+        <v>4.7257889999999998</v>
+      </c>
+      <c r="L9">
+        <v>744.831591</v>
+      </c>
+      <c r="M9">
+        <v>6.4267309999999998E-3</v>
+      </c>
+      <c r="N9">
+        <v>6.7507410000000002E-3</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>26.979769659999999</v>
+      </c>
+      <c r="E10">
+        <v>137812.66339999999</v>
+      </c>
+      <c r="F10">
+        <v>136210.7084</v>
+      </c>
+      <c r="G10">
+        <v>1601.954999</v>
+      </c>
+      <c r="H10">
+        <v>137812.66339999999</v>
+      </c>
+      <c r="I10">
+        <v>4.7720000000000002</v>
+      </c>
+      <c r="J10">
+        <v>938.3</v>
+      </c>
+      <c r="K10">
+        <v>4.4773643999999999</v>
+      </c>
+      <c r="L10">
+        <v>647.64238850000004</v>
+      </c>
+      <c r="M10">
+        <v>9.1061219999999995E-3</v>
+      </c>
+      <c r="N10">
+        <v>1.2847614E-2</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>25.958250750000001</v>
+      </c>
+      <c r="E11">
+        <v>204187.6004</v>
+      </c>
+      <c r="F11">
+        <v>202343.58009999999</v>
+      </c>
+      <c r="G11">
+        <v>1844.0203120000001</v>
+      </c>
+      <c r="H11">
+        <v>204187.6004</v>
+      </c>
+      <c r="I11">
+        <v>4.8120000000000003</v>
+      </c>
+      <c r="J11">
+        <v>838.85</v>
+      </c>
+      <c r="K11">
+        <v>4.0311442</v>
+      </c>
+      <c r="L11">
+        <v>849.67365229999996</v>
+      </c>
+      <c r="M11">
+        <v>1.0055427E-2</v>
+      </c>
+      <c r="N11">
+        <v>1.1283712E-2</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12">
+        <v>25.274220710000002</v>
+      </c>
+      <c r="E12">
+        <v>226810.8566</v>
+      </c>
+      <c r="F12">
+        <v>224721.8438</v>
+      </c>
+      <c r="G12">
+        <v>2089.0128119999999</v>
+      </c>
+      <c r="H12">
+        <v>226810.8566</v>
+      </c>
+      <c r="I12">
+        <v>4.84</v>
+      </c>
+      <c r="J12">
+        <v>724.3</v>
+      </c>
+      <c r="K12">
+        <v>3.50536</v>
+      </c>
+      <c r="L12">
+        <v>819.74987109999995</v>
+      </c>
+      <c r="M12">
+        <v>5.057817E-3</v>
+      </c>
+      <c r="N12">
+        <v>7.1550570000000003E-3</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13">
+        <v>25.337324379999998</v>
+      </c>
+      <c r="E13">
+        <v>148628.74479999999</v>
+      </c>
+      <c r="F13">
+        <v>147115.9307</v>
+      </c>
+      <c r="G13">
+        <v>1512.814114</v>
+      </c>
+      <c r="H13">
+        <v>148628.74479999999</v>
+      </c>
+      <c r="I13">
+        <v>4.8259999999999996</v>
+      </c>
+      <c r="J13">
+        <v>778.85</v>
+      </c>
+      <c r="K13">
+        <v>3.7581722000000002</v>
+      </c>
+      <c r="L13">
+        <v>584.6553758</v>
+      </c>
+      <c r="M13">
+        <v>1.5513964E-2</v>
+      </c>
+      <c r="N13">
+        <v>1.5435636000000001E-2</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14">
+        <v>25.240949659999998</v>
+      </c>
+      <c r="E14">
+        <v>191528.326</v>
+      </c>
+      <c r="F14">
+        <v>189663.66620000001</v>
+      </c>
+      <c r="G14">
+        <v>1864.659791</v>
+      </c>
+      <c r="H14">
+        <v>191528.326</v>
+      </c>
+      <c r="I14">
+        <v>4.8479999999999999</v>
+      </c>
+      <c r="J14">
+        <v>730.9</v>
+      </c>
+      <c r="K14">
+        <v>3.5430131999999999</v>
+      </c>
+      <c r="L14">
+        <v>701.50001689999999</v>
+      </c>
+      <c r="M14">
+        <v>2.7911729999999999E-2</v>
+      </c>
+      <c r="N14">
+        <v>2.8468778E-2</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15">
+        <v>25.204348400000001</v>
+      </c>
+      <c r="E15">
+        <v>216127.28750000001</v>
+      </c>
+      <c r="F15">
+        <v>214126.5215</v>
+      </c>
+      <c r="G15">
+        <v>2000.7660410000001</v>
+      </c>
+      <c r="H15">
+        <v>216127.28750000001</v>
+      </c>
+      <c r="I15">
+        <v>4.8520000000000003</v>
+      </c>
+      <c r="J15">
+        <v>725</v>
+      </c>
+      <c r="K15">
+        <v>3.5177</v>
+      </c>
+      <c r="L15">
+        <v>785.02283320000004</v>
+      </c>
+      <c r="M15">
+        <v>1.5132280999999999E-2</v>
+      </c>
+      <c r="N15">
+        <v>2.5868919000000001E-2</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16">
+        <v>25.300291359999999</v>
+      </c>
+      <c r="E16">
+        <v>141327.4276</v>
+      </c>
+      <c r="F16">
+        <v>139868.62950000001</v>
+      </c>
+      <c r="G16">
+        <v>1458.7980210000001</v>
+      </c>
+      <c r="H16">
+        <v>141327.4276</v>
+      </c>
+      <c r="I16">
+        <v>4.8360000000000003</v>
+      </c>
+      <c r="J16">
+        <v>794.3</v>
+      </c>
+      <c r="K16">
+        <v>3.8414003999999999</v>
+      </c>
+      <c r="L16">
+        <v>568.7604748</v>
+      </c>
+      <c r="M16">
+        <v>6.4267309999999998E-3</v>
+      </c>
+      <c r="N16">
+        <v>6.7507410000000002E-3</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>25.22401185</v>
+      </c>
+      <c r="E17">
+        <v>208400.78589999999</v>
+      </c>
+      <c r="F17">
+        <v>206421.30300000001</v>
+      </c>
+      <c r="G17">
+        <v>1979.4829159999999</v>
+      </c>
+      <c r="H17">
+        <v>208400.78589999999</v>
+      </c>
+      <c r="I17">
+        <v>4.8659999999999997</v>
+      </c>
+      <c r="J17">
+        <v>693</v>
+      </c>
+      <c r="K17">
+        <v>3.3720460000000001</v>
+      </c>
+      <c r="L17">
+        <v>726.52795630000003</v>
+      </c>
+      <c r="M17">
+        <v>2.9066314999999999E-2</v>
+      </c>
+      <c r="N17">
+        <v>4.6810307000000002E-2</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18">
+        <v>25.40069171</v>
+      </c>
+      <c r="E18">
+        <v>129746.7332</v>
+      </c>
+      <c r="F18">
+        <v>128354.0405</v>
+      </c>
+      <c r="G18">
+        <v>1392.6927599999999</v>
+      </c>
+      <c r="H18">
+        <v>129746.7332</v>
+      </c>
+      <c r="I18">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="J18">
+        <v>719.65</v>
+      </c>
+      <c r="K18">
+        <v>3.4902541999999999</v>
+      </c>
+      <c r="L18">
+        <v>476.15412980000002</v>
+      </c>
+      <c r="M18">
+        <v>9.1061219999999995E-3</v>
+      </c>
+      <c r="N18">
+        <v>1.2847614E-2</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>25.29606725</v>
+      </c>
+      <c r="E19">
+        <v>224907.3339</v>
+      </c>
+      <c r="F19">
+        <v>222850.85149999999</v>
+      </c>
+      <c r="G19">
+        <v>2056.4824469999999</v>
+      </c>
+      <c r="H19">
+        <v>224907.3339</v>
+      </c>
+      <c r="I19">
+        <v>4.8259999999999996</v>
+      </c>
+      <c r="J19">
+        <v>764.3</v>
+      </c>
+      <c r="K19">
+        <v>3.6878422</v>
+      </c>
+      <c r="L19">
+        <v>853.32828340000003</v>
+      </c>
+      <c r="M19">
+        <v>2.0769076000000001E-2</v>
+      </c>
+      <c r="N19">
+        <v>1.7173126E-2</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20">
+        <v>25.24190497</v>
+      </c>
+      <c r="E20">
+        <v>198552.82449999999</v>
+      </c>
+      <c r="F20">
+        <v>196702.1741</v>
+      </c>
+      <c r="G20">
+        <v>1850.650416</v>
+      </c>
+      <c r="H20">
+        <v>198552.82449999999</v>
+      </c>
+      <c r="I20">
+        <v>4.8419999999999996</v>
+      </c>
+      <c r="J20">
+        <v>713.6</v>
+      </c>
+      <c r="K20">
+        <v>3.4548928000000001</v>
+      </c>
+      <c r="L20">
+        <v>709.27223379999998</v>
+      </c>
+      <c r="M20">
+        <v>1.0055427E-2</v>
+      </c>
+      <c r="N20">
+        <v>1.1283712E-2</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21">
+        <v>25.24018877</v>
+      </c>
+      <c r="E21">
+        <v>148058.9473</v>
+      </c>
+      <c r="F21">
+        <v>146532.38269999999</v>
+      </c>
+      <c r="G21">
+        <v>1526.564635</v>
+      </c>
+      <c r="H21">
+        <v>148058.9473</v>
+      </c>
+      <c r="I21">
+        <v>4.8440000000000003</v>
+      </c>
+      <c r="J21">
+        <v>737.5</v>
+      </c>
+      <c r="K21">
+        <v>3.5724499999999999</v>
+      </c>
+      <c r="L21">
+        <v>553.43411149999997</v>
+      </c>
+      <c r="M21">
+        <v>1.5513964E-2</v>
+      </c>
+      <c r="N21">
+        <v>1.5435636000000001E-2</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22">
+        <v>25.29232764</v>
+      </c>
+      <c r="E22">
+        <v>141282.94219999999</v>
+      </c>
+      <c r="F22">
+        <v>139828.67929999999</v>
+      </c>
+      <c r="G22">
+        <v>1454.2629159999999</v>
+      </c>
+      <c r="H22">
+        <v>141282.94219999999</v>
+      </c>
+      <c r="I22">
+        <v>4.8440000000000003</v>
+      </c>
+      <c r="J22">
+        <v>715.2</v>
+      </c>
+      <c r="K22">
+        <v>3.4643440000000001</v>
+      </c>
+      <c r="L22">
+        <v>512.61696949999998</v>
+      </c>
+      <c r="M22">
+        <v>6.4267309999999998E-3</v>
+      </c>
+      <c r="N22">
+        <v>6.7507410000000002E-3</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23">
+        <v>25.203056069999999</v>
+      </c>
+      <c r="E23">
+        <v>226172.22519999999</v>
+      </c>
+      <c r="F23">
+        <v>224098.08369999999</v>
+      </c>
+      <c r="G23">
+        <v>2074.141509</v>
+      </c>
+      <c r="H23">
+        <v>226172.22519999999</v>
+      </c>
+      <c r="I23">
+        <v>4.8559999999999999</v>
+      </c>
+      <c r="J23">
+        <v>698.4</v>
+      </c>
+      <c r="K23">
+        <v>3.3913395999999998</v>
+      </c>
+      <c r="L23">
+        <v>795.10236320000001</v>
+      </c>
+      <c r="M23">
+        <v>5.057817E-3</v>
+      </c>
+      <c r="N23">
+        <v>7.1550570000000003E-3</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24">
+        <v>25.171407909999999</v>
+      </c>
+      <c r="E24">
+        <v>223798.9877</v>
+      </c>
+      <c r="F24">
+        <v>221755.2218</v>
+      </c>
+      <c r="G24">
+        <v>2043.765936</v>
+      </c>
+      <c r="H24">
+        <v>223798.9877</v>
+      </c>
+      <c r="I24">
+        <v>4.8620000000000001</v>
+      </c>
+      <c r="J24">
+        <v>692.85</v>
+      </c>
+      <c r="K24">
+        <v>3.3679770000000002</v>
+      </c>
+      <c r="L24">
+        <v>777.15812789999995</v>
+      </c>
+      <c r="M24">
+        <v>2.0769076000000001E-2</v>
+      </c>
+      <c r="N24">
+        <v>1.7173126E-2</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25">
+        <v>25.306343089999999</v>
+      </c>
+      <c r="E25">
+        <v>192024.53140000001</v>
+      </c>
+      <c r="F25">
+        <v>190213.71030000001</v>
+      </c>
+      <c r="G25">
+        <v>1810.8210409999999</v>
+      </c>
+      <c r="H25">
+        <v>192024.53140000001</v>
+      </c>
+      <c r="I25">
+        <v>4.8419999999999996</v>
+      </c>
+      <c r="J25">
+        <v>725</v>
+      </c>
+      <c r="K25">
+        <v>3.5102159999999998</v>
+      </c>
+      <c r="L25">
+        <v>697.20729449999999</v>
+      </c>
+      <c r="M25">
+        <v>2.7911729999999999E-2</v>
+      </c>
+      <c r="N25">
+        <v>2.8468778E-2</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26">
+        <v>25.249635609999999</v>
+      </c>
+      <c r="E26">
+        <v>208612.4895</v>
+      </c>
+      <c r="F26">
+        <v>206646.28419999999</v>
+      </c>
+      <c r="G26">
+        <v>1966.205207</v>
+      </c>
+      <c r="H26">
+        <v>208612.4895</v>
+      </c>
+      <c r="I26">
+        <v>4.8639999999999999</v>
+      </c>
+      <c r="J26">
+        <v>690.95</v>
+      </c>
+      <c r="K26">
+        <v>3.3604091999999999</v>
+      </c>
+      <c r="L26">
+        <v>724.9895262</v>
+      </c>
+      <c r="M26">
+        <v>2.9066314999999999E-2</v>
+      </c>
+      <c r="N26">
+        <v>4.6810307000000002E-2</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27">
+        <v>25.245788019999999</v>
+      </c>
+      <c r="E27">
+        <v>216482.6323</v>
+      </c>
+      <c r="F27">
+        <v>214480.6617</v>
+      </c>
+      <c r="G27">
+        <v>2001.9705200000001</v>
+      </c>
+      <c r="H27">
+        <v>216482.6323</v>
+      </c>
+      <c r="I27">
+        <v>4.8479999999999999</v>
+      </c>
+      <c r="J27">
+        <v>730.8</v>
+      </c>
+      <c r="K27">
+        <v>3.5416683999999998</v>
+      </c>
+      <c r="L27">
+        <v>789.90926739999998</v>
+      </c>
+      <c r="M27">
+        <v>1.5132280999999999E-2</v>
+      </c>
+      <c r="N27">
+        <v>2.5868919000000001E-2</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28">
+        <v>25.35047986</v>
+      </c>
+      <c r="E28">
+        <v>129490.25109999999</v>
+      </c>
+      <c r="F28">
+        <v>128076.7916</v>
+      </c>
+      <c r="G28">
+        <v>1413.4595830000001</v>
+      </c>
+      <c r="H28">
+        <v>129490.25109999999</v>
+      </c>
+      <c r="I28">
+        <v>4.8440000000000003</v>
+      </c>
+      <c r="J28">
+        <v>719.15</v>
+      </c>
+      <c r="K28">
+        <v>3.4834022</v>
+      </c>
+      <c r="L28">
+        <v>475.5064658</v>
+      </c>
+      <c r="M28">
+        <v>9.1061219999999995E-3</v>
+      </c>
+      <c r="N28">
+        <v>1.2847614E-2</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29">
+        <v>25.245883209999999</v>
+      </c>
+      <c r="E29">
+        <v>208581.4871</v>
+      </c>
+      <c r="F29">
+        <v>206587.09020000001</v>
+      </c>
+      <c r="G29">
+        <v>1994.3968219999999</v>
+      </c>
+      <c r="H29">
+        <v>208581.4871</v>
+      </c>
+      <c r="I29">
+        <v>4.8559999999999999</v>
+      </c>
+      <c r="J29">
+        <v>726.55</v>
+      </c>
+      <c r="K29">
+        <v>3.5275547999999999</v>
+      </c>
+      <c r="L29">
+        <v>758.70413599999995</v>
+      </c>
+      <c r="M29">
+        <v>2.9066314999999999E-2</v>
+      </c>
+      <c r="N29">
+        <v>4.6810307000000002E-2</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30">
+        <v>25.30281188</v>
+      </c>
+      <c r="E30">
+        <v>224967.30040000001</v>
+      </c>
+      <c r="F30">
+        <v>222909.0097</v>
+      </c>
+      <c r="G30">
+        <v>2058.2907799999998</v>
+      </c>
+      <c r="H30">
+        <v>224967.30040000001</v>
+      </c>
+      <c r="I30">
+        <v>4.8419999999999996</v>
+      </c>
+      <c r="J30">
+        <v>738.9</v>
+      </c>
+      <c r="K30">
+        <v>3.5777754000000002</v>
+      </c>
+      <c r="L30">
+        <v>828.09498840000003</v>
+      </c>
+      <c r="M30">
+        <v>2.0769076000000001E-2</v>
+      </c>
+      <c r="N30">
+        <v>1.7173126E-2</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31">
+        <v>25.299871580000001</v>
+      </c>
+      <c r="E31">
+        <v>227041.04749999999</v>
+      </c>
+      <c r="F31">
+        <v>224980.17230000001</v>
+      </c>
+      <c r="G31">
+        <v>2060.8752589999999</v>
+      </c>
+      <c r="H31">
+        <v>227041.04749999999</v>
+      </c>
+      <c r="I31">
+        <v>4.8620000000000001</v>
+      </c>
+      <c r="J31">
+        <v>671.5</v>
+      </c>
+      <c r="K31">
+        <v>3.2648429999999999</v>
+      </c>
+      <c r="L31">
+        <v>762.84888939999996</v>
+      </c>
+      <c r="M31">
+        <v>5.057817E-3</v>
+      </c>
+      <c r="N31">
+        <v>7.1550570000000003E-3</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32">
+        <v>25.253354009999999</v>
+      </c>
+      <c r="E32">
+        <v>216547.51060000001</v>
+      </c>
+      <c r="F32">
+        <v>214472.23180000001</v>
+      </c>
+      <c r="G32">
+        <v>2075.2788009999999</v>
+      </c>
+      <c r="H32">
+        <v>216547.51060000001</v>
+      </c>
+      <c r="I32">
+        <v>4.84</v>
+      </c>
+      <c r="J32">
+        <v>771.5</v>
+      </c>
+      <c r="K32">
+        <v>3.7316479999999999</v>
+      </c>
+      <c r="L32">
+        <v>833.39724869999998</v>
+      </c>
+      <c r="M32">
+        <v>1.5132280999999999E-2</v>
+      </c>
+      <c r="N32">
+        <v>2.5868919000000001E-2</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>25.304317439999998</v>
+      </c>
+      <c r="E33">
+        <v>199043.761</v>
+      </c>
+      <c r="F33">
+        <v>197191.4137</v>
+      </c>
+      <c r="G33">
+        <v>1852.347291</v>
+      </c>
+      <c r="H33">
+        <v>199043.761</v>
+      </c>
+      <c r="I33">
+        <v>4.83</v>
+      </c>
+      <c r="J33">
+        <v>751.55</v>
+      </c>
+      <c r="K33">
+        <v>3.6293446</v>
+      </c>
+      <c r="L33">
+        <v>746.5009933</v>
+      </c>
+      <c r="M33">
+        <v>1.0055427E-2</v>
+      </c>
+      <c r="N33">
+        <v>1.1283712E-2</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34">
+        <v>25.332996789999999</v>
+      </c>
+      <c r="E34">
+        <v>148603.35920000001</v>
+      </c>
+      <c r="F34">
+        <v>147088.8866</v>
+      </c>
+      <c r="G34">
+        <v>1514.472604</v>
+      </c>
+      <c r="H34">
+        <v>148603.35920000001</v>
+      </c>
+      <c r="I34">
+        <v>4.8280000000000003</v>
+      </c>
+      <c r="J34">
+        <v>769.6</v>
+      </c>
+      <c r="K34">
+        <v>3.7153323999999999</v>
+      </c>
+      <c r="L34">
+        <v>574.86605740000005</v>
+      </c>
+      <c r="M34">
+        <v>1.5513964E-2</v>
+      </c>
+      <c r="N34">
+        <v>1.5435636000000001E-2</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35">
+        <v>25.256146810000001</v>
+      </c>
+      <c r="E35">
+        <v>191643.64199999999</v>
+      </c>
+      <c r="F35">
+        <v>189796.73560000001</v>
+      </c>
+      <c r="G35">
+        <v>1846.9063530000001</v>
+      </c>
+      <c r="H35">
+        <v>191643.64199999999</v>
+      </c>
+      <c r="I35">
+        <v>4.8520000000000003</v>
+      </c>
+      <c r="J35">
+        <v>728.8</v>
+      </c>
+      <c r="K35">
+        <v>3.5360640000000001</v>
+      </c>
+      <c r="L35">
+        <v>699.04628639999999</v>
+      </c>
+      <c r="M35">
+        <v>2.7911729999999999E-2</v>
+      </c>
+      <c r="N35">
+        <v>2.8468778E-2</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36">
+        <v>25.376467869999999</v>
+      </c>
+      <c r="E36">
+        <v>141752.94949999999</v>
+      </c>
+      <c r="F36">
+        <v>140326.82939999999</v>
+      </c>
+      <c r="G36">
+        <v>1426.120156</v>
+      </c>
+      <c r="H36">
+        <v>141752.94949999999</v>
+      </c>
+      <c r="I36">
+        <v>4.8520000000000003</v>
+      </c>
+      <c r="J36">
+        <v>715.6</v>
+      </c>
+      <c r="K36">
+        <v>3.4716192000000001</v>
+      </c>
+      <c r="L36">
+        <v>516.21087060000002</v>
+      </c>
+      <c r="M36">
+        <v>6.4267309999999998E-3</v>
+      </c>
+      <c r="N36">
+        <v>6.7507410000000002E-3</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37">
+        <v>25.295908449999999</v>
+      </c>
+      <c r="E37">
+        <v>129211.5004</v>
+      </c>
+      <c r="F37">
+        <v>127786.38280000001</v>
+      </c>
+      <c r="G37">
+        <v>1425.1176029999999</v>
+      </c>
+      <c r="H37">
+        <v>129211.5004</v>
+      </c>
+      <c r="I37">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="J37">
+        <v>681.55</v>
+      </c>
+      <c r="K37">
+        <v>3.3123330000000002</v>
+      </c>
+      <c r="L37">
+        <v>449.55910139999997</v>
+      </c>
+      <c r="M37">
+        <v>9.1061219999999995E-3</v>
+      </c>
+      <c r="N37">
+        <v>1.2847614E-2</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>25.234096399999999</v>
+      </c>
+      <c r="E38">
+        <v>198491.40229999999</v>
+      </c>
+      <c r="F38">
+        <v>196655.1213</v>
+      </c>
+      <c r="G38">
+        <v>1836.2809890000001</v>
+      </c>
+      <c r="H38">
+        <v>198491.40229999999</v>
+      </c>
+      <c r="I38">
+        <v>4.8419999999999996</v>
+      </c>
+      <c r="J38">
+        <v>699.4</v>
+      </c>
+      <c r="K38">
+        <v>3.3862193999999999</v>
+      </c>
+      <c r="L38">
+        <v>693.46215940000002</v>
+      </c>
+      <c r="M38">
+        <v>1.0055427E-2</v>
+      </c>
+      <c r="N38">
+        <v>1.1283712E-2</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39">
+        <v>25.253249199999999</v>
+      </c>
+      <c r="E39">
+        <v>226622.65839999999</v>
+      </c>
+      <c r="F39">
+        <v>224502.2977</v>
+      </c>
+      <c r="G39">
+        <v>2120.3606239999999</v>
+      </c>
+      <c r="H39">
+        <v>226622.65839999999</v>
+      </c>
+      <c r="I39">
+        <v>4.84</v>
+      </c>
+      <c r="J39">
+        <v>721.85</v>
+      </c>
+      <c r="K39">
+        <v>3.492651</v>
+      </c>
+      <c r="L39">
+        <v>813.70043239999995</v>
+      </c>
+      <c r="M39">
+        <v>5.057817E-3</v>
+      </c>
+      <c r="N39">
+        <v>7.1550570000000003E-3</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40">
+        <v>25.323139430000001</v>
+      </c>
+      <c r="E40">
+        <v>148545.53589999999</v>
+      </c>
+      <c r="F40">
+        <v>147042.72940000001</v>
+      </c>
+      <c r="G40">
+        <v>1502.806458</v>
+      </c>
+      <c r="H40">
+        <v>148545.53589999999</v>
+      </c>
+      <c r="I40">
+        <v>4.82</v>
+      </c>
+      <c r="J40">
+        <v>780.15</v>
+      </c>
+      <c r="K40">
+        <v>3.7599876000000001</v>
+      </c>
+      <c r="L40">
+        <v>584.37321569999995</v>
+      </c>
+      <c r="M40">
+        <v>1.5513964E-2</v>
+      </c>
+      <c r="N40">
+        <v>1.5435636000000001E-2</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41">
+        <v>25.2586944</v>
+      </c>
+      <c r="E41">
+        <v>191662.9731</v>
+      </c>
+      <c r="F41">
+        <v>189878.84820000001</v>
+      </c>
+      <c r="G41">
+        <v>1784.1248949999999</v>
+      </c>
+      <c r="H41">
+        <v>191662.9731</v>
+      </c>
+      <c r="I41">
+        <v>4.8479999999999999</v>
+      </c>
+      <c r="J41">
+        <v>755.75</v>
+      </c>
+      <c r="K41">
+        <v>3.6636291999999999</v>
+      </c>
+      <c r="L41">
+        <v>725.6739225</v>
+      </c>
+      <c r="M41">
+        <v>2.7911729999999999E-2</v>
+      </c>
+      <c r="N41">
+        <v>2.8468778E-2</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42">
+        <v>25.288720519999998</v>
+      </c>
+      <c r="E42">
+        <v>216850.77849999999</v>
+      </c>
+      <c r="F42">
+        <v>214800.7585</v>
+      </c>
+      <c r="G42">
+        <v>2050.0199990000001</v>
+      </c>
+      <c r="H42">
+        <v>216850.77849999999</v>
+      </c>
+      <c r="I42">
+        <v>4.8479999999999999</v>
+      </c>
+      <c r="J42">
+        <v>705.95</v>
+      </c>
+      <c r="K42">
+        <v>3.4219374</v>
+      </c>
+      <c r="L42">
+        <v>766.10646640000004</v>
+      </c>
+      <c r="M42">
+        <v>1.5132280999999999E-2</v>
+      </c>
+      <c r="N42">
+        <v>2.5868919000000001E-2</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43">
+        <v>42</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43">
+        <v>25.351184109999998</v>
+      </c>
+      <c r="E43">
+        <v>141611.7144</v>
+      </c>
+      <c r="F43">
+        <v>140155.63750000001</v>
+      </c>
+      <c r="G43">
+        <v>1456.076926</v>
+      </c>
+      <c r="H43">
+        <v>141611.7144</v>
+      </c>
+      <c r="I43">
+        <v>4.84</v>
+      </c>
+      <c r="J43">
+        <v>725.25</v>
+      </c>
+      <c r="K43">
+        <v>3.5089980000000001</v>
+      </c>
+      <c r="L43">
+        <v>519.65144989999999</v>
+      </c>
+      <c r="M43">
+        <v>6.4267309999999998E-3</v>
+      </c>
+      <c r="N43">
+        <v>6.7507410000000002E-3</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44">
+        <v>25.26861061</v>
+      </c>
+      <c r="E44">
+        <v>208769.26089999999</v>
+      </c>
+      <c r="F44">
+        <v>206820.95430000001</v>
+      </c>
+      <c r="G44">
+        <v>1948.306562</v>
+      </c>
+      <c r="H44">
+        <v>208769.26089999999</v>
+      </c>
+      <c r="I44">
+        <v>4.8460000000000001</v>
+      </c>
+      <c r="J44">
+        <v>722.4</v>
+      </c>
+      <c r="K44">
+        <v>3.4992033999999999</v>
+      </c>
+      <c r="L44">
+        <v>753.22862380000004</v>
+      </c>
+      <c r="M44">
+        <v>2.9066314999999999E-2</v>
+      </c>
+      <c r="N44">
+        <v>4.6810307000000002E-2</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45">
+        <v>44</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45">
+        <v>25.432499580000002</v>
+      </c>
+      <c r="E45">
+        <v>129909.20789999999</v>
+      </c>
+      <c r="F45">
+        <v>128468.1865</v>
+      </c>
+      <c r="G45">
+        <v>1441.0213530000001</v>
+      </c>
+      <c r="H45">
+        <v>129909.20789999999</v>
+      </c>
+      <c r="I45">
+        <v>4.8419999999999996</v>
+      </c>
+      <c r="J45">
+        <v>747</v>
+      </c>
+      <c r="K45">
+        <v>3.6169419999999999</v>
+      </c>
+      <c r="L45">
+        <v>494.14027060000001</v>
+      </c>
+      <c r="M45">
+        <v>9.1061219999999995E-3</v>
+      </c>
+      <c r="N45">
+        <v>1.2847614E-2</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46">
+        <v>25.279947029999999</v>
+      </c>
+      <c r="E46">
+        <v>224764.0091</v>
+      </c>
+      <c r="F46">
+        <v>222673.9926</v>
+      </c>
+      <c r="G46">
+        <v>2090.0165099999999</v>
+      </c>
+      <c r="H46">
+        <v>224764.0091</v>
+      </c>
+      <c r="I46">
+        <v>4.8280000000000003</v>
+      </c>
+      <c r="J46">
+        <v>749.25</v>
+      </c>
+      <c r="K46">
+        <v>3.6167189999999998</v>
+      </c>
+      <c r="L46">
+        <v>843.20396600000004</v>
+      </c>
+      <c r="M46">
+        <v>2.0769076000000001E-2</v>
+      </c>
+      <c r="N46">
+        <v>1.7173126E-2</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47">
+        <v>25.368164310000001</v>
+      </c>
+      <c r="E47">
+        <v>199545.9804</v>
+      </c>
+      <c r="F47">
+        <v>197685.28330000001</v>
+      </c>
+      <c r="G47">
+        <v>1860.697187</v>
+      </c>
+      <c r="H47">
+        <v>199545.9804</v>
+      </c>
+      <c r="I47">
+        <v>4.8540000000000001</v>
+      </c>
+      <c r="J47">
+        <v>778.15</v>
+      </c>
+      <c r="K47">
+        <v>3.7769466</v>
+      </c>
+      <c r="L47">
+        <v>778.16651679999995</v>
+      </c>
+      <c r="M47">
+        <v>1.0055427E-2</v>
+      </c>
+      <c r="N47">
+        <v>1.1283712E-2</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48">
+        <v>25.291364470000001</v>
+      </c>
+      <c r="E48">
+        <v>148359.144</v>
+      </c>
+      <c r="F48">
+        <v>146837.0785</v>
+      </c>
+      <c r="G48">
+        <v>1522.0654159999999</v>
+      </c>
+      <c r="H48">
+        <v>148359.144</v>
+      </c>
+      <c r="I48">
+        <v>4.8280000000000003</v>
+      </c>
+      <c r="J48">
+        <v>760.1</v>
+      </c>
+      <c r="K48">
+        <v>3.6698012000000002</v>
+      </c>
+      <c r="L48">
+        <v>567.82152150000002</v>
+      </c>
+      <c r="M48">
+        <v>1.5513964E-2</v>
+      </c>
+      <c r="N48">
+        <v>1.5435636000000001E-2</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49">
+        <v>48</v>
+      </c>
+      <c r="C49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49">
+        <v>25.44802834</v>
+      </c>
+      <c r="E49">
+        <v>142152.6863</v>
+      </c>
+      <c r="F49">
+        <v>140732.22029999999</v>
+      </c>
+      <c r="G49">
+        <v>1420.4660409999999</v>
+      </c>
+      <c r="H49">
+        <v>142152.6863</v>
+      </c>
+      <c r="I49">
+        <v>4.8360000000000003</v>
+      </c>
+      <c r="J49">
+        <v>763.45</v>
+      </c>
+      <c r="K49">
+        <v>3.6919632</v>
+      </c>
+      <c r="L49">
+        <v>546.74708740000005</v>
+      </c>
+      <c r="M49">
+        <v>6.4267309999999998E-3</v>
+      </c>
+      <c r="N49">
+        <v>6.7507410000000002E-3</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50">
+        <v>49</v>
+      </c>
+      <c r="C50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50">
+        <v>25.289153249999998</v>
+      </c>
+      <c r="E50">
+        <v>226944.86129999999</v>
+      </c>
+      <c r="F50">
+        <v>224801.01689999999</v>
+      </c>
+      <c r="G50">
+        <v>2143.8443219999999</v>
+      </c>
+      <c r="H50">
+        <v>226944.86129999999</v>
+      </c>
+      <c r="I50">
+        <v>4.8339999999999996</v>
+      </c>
+      <c r="J50">
+        <v>735.55</v>
+      </c>
+      <c r="K50">
+        <v>3.5554191999999998</v>
+      </c>
+      <c r="L50">
+        <v>829.25481430000002</v>
+      </c>
+      <c r="M50">
+        <v>5.057817E-3</v>
+      </c>
+      <c r="N50">
+        <v>7.1550570000000003E-3</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51">
+        <v>25.334429929999999</v>
+      </c>
+      <c r="E51">
+        <v>225248.41649999999</v>
+      </c>
+      <c r="F51">
+        <v>223146.6605</v>
+      </c>
+      <c r="G51">
+        <v>2101.7559890000002</v>
+      </c>
+      <c r="H51">
+        <v>225248.41649999999</v>
+      </c>
+      <c r="I51">
+        <v>4.8259999999999996</v>
+      </c>
+      <c r="J51">
+        <v>772.35</v>
+      </c>
+      <c r="K51">
+        <v>3.7263972000000001</v>
+      </c>
+      <c r="L51">
+        <v>864.37094930000001</v>
+      </c>
+      <c r="M51">
+        <v>2.0769076000000001E-2</v>
+      </c>
+      <c r="N51">
+        <v>1.7173126E-2</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D52">
+        <v>25.612589629999999</v>
+      </c>
+      <c r="H52">
+        <v>189887.0681</v>
+      </c>
+      <c r="K52">
+        <v>3.7708611080000001</v>
+      </c>
+      <c r="L52">
+        <v>744.81110179999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/paper/results.xlsx
+++ b/paper/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/71600677250d0614/Documents/MTech/Thesis/Yolov26_experiments_raspberryPi/ronin_yolov26/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9091D59E-E410-46CB-80C3-50A39B8B3F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94620AFA-51E9-459A-8831-8436E2121F7B}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{9091D59E-E410-46CB-80C3-50A39B8B3F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C61454D3-30CF-4C72-ACF7-101CCDFE5389}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{1B44670D-8AB3-4C03-85DD-5F85B107A258}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="8" xr2:uid="{1B44670D-8AB3-4C03-85DD-5F85B107A258}"/>
   </bookViews>
   <sheets>
     <sheet name="Tinycnn_random" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="shufflenet" sheetId="8" r:id="rId6"/>
     <sheet name="All results " sheetId="5" r:id="rId7"/>
     <sheet name="yolo26_eff_rf_random_benchmark_" sheetId="10" r:id="rId8"/>
+    <sheet name="llio128" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="38">
   <si>
     <t>model</t>
   </si>
@@ -154,6 +155,9 @@
   </si>
   <si>
     <t>yolo26_eff_A_rf</t>
+  </si>
+  <si>
+    <t>llio128</t>
   </si>
 </sst>
 </file>
@@ -20641,4 +20645,2411 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424BF16C-FC26-434B-B01F-492A1A751018}">
+  <dimension ref="A1:O51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>17.6333075175502</v>
+      </c>
+      <c r="E2">
+        <v>145686.38670999999</v>
+      </c>
+      <c r="F2">
+        <v>145686.38670999999</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>145686.38670999999</v>
+      </c>
+      <c r="I2">
+        <v>4.6319999999999997</v>
+      </c>
+      <c r="J2">
+        <v>1247.05</v>
+      </c>
+      <c r="K2">
+        <v>5.7751766</v>
+      </c>
+      <c r="L2">
+        <v>843.02261132847195</v>
+      </c>
+      <c r="M2">
+        <v>5.18991760909557E-2</v>
+      </c>
+      <c r="N2">
+        <v>8.4807902574539101E-2</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>17.6363408970869</v>
+      </c>
+      <c r="E3">
+        <v>156804.706916</v>
+      </c>
+      <c r="F3">
+        <v>156804.706916</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>156804.706916</v>
+      </c>
+      <c r="I3">
+        <v>4.6719999999999997</v>
+      </c>
+      <c r="J3">
+        <v>1071.5999999999999</v>
+      </c>
+      <c r="K3">
+        <v>5.0047263999999902</v>
+      </c>
+      <c r="L3">
+        <v>785.17488608752001</v>
+      </c>
+      <c r="M3">
+        <v>2.8086921200156201E-2</v>
+      </c>
+      <c r="N3">
+        <v>2.6280906051397299E-2</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>17.700581762759001</v>
+      </c>
+      <c r="E4">
+        <v>158845.02073899901</v>
+      </c>
+      <c r="F4">
+        <v>158845.02073899901</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>158845.02073899901</v>
+      </c>
+      <c r="I4">
+        <v>4.68</v>
+      </c>
+      <c r="J4">
+        <v>1111</v>
+      </c>
+      <c r="K4">
+        <v>5.1993847999999998</v>
+      </c>
+      <c r="L4">
+        <v>826.32750734748004</v>
+      </c>
+      <c r="M4">
+        <v>7.3200054466724396E-3</v>
+      </c>
+      <c r="N4">
+        <v>7.0026395842432898E-3</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>17.759727885714199</v>
+      </c>
+      <c r="E5">
+        <v>152289.66662</v>
+      </c>
+      <c r="F5">
+        <v>152289.66662</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>152289.66662</v>
+      </c>
+      <c r="I5">
+        <v>4.6639999999999997</v>
+      </c>
+      <c r="J5">
+        <v>1099.3999999999901</v>
+      </c>
+      <c r="K5">
+        <v>5.1270975999999902</v>
+      </c>
+      <c r="L5">
+        <v>781.22771239814597</v>
+      </c>
+      <c r="M5">
+        <v>3.6901112645864403E-2</v>
+      </c>
+      <c r="N5">
+        <v>5.2505973726511002E-2</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>17.623682166285199</v>
+      </c>
+      <c r="E6">
+        <v>138627.88391999999</v>
+      </c>
+      <c r="F6">
+        <v>138627.88391999999</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>138627.88391999999</v>
+      </c>
+      <c r="I6">
+        <v>4.6239999999999997</v>
+      </c>
+      <c r="J6">
+        <v>1113.8999999999901</v>
+      </c>
+      <c r="K6">
+        <v>5.1503295999999903</v>
+      </c>
+      <c r="L6">
+        <v>714.36480069804304</v>
+      </c>
+      <c r="M6">
+        <v>1.53279257938265E-2</v>
+      </c>
+      <c r="N6">
+        <v>2.2899296134710301E-2</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>17.620762435731301</v>
+      </c>
+      <c r="E7">
+        <v>103363.392448</v>
+      </c>
+      <c r="F7">
+        <v>103363.392448</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>103363.392448</v>
+      </c>
+      <c r="I7">
+        <v>4.62</v>
+      </c>
+      <c r="J7">
+        <v>1165.94999999999</v>
+      </c>
+      <c r="K7">
+        <v>5.3814916000000004</v>
+      </c>
+      <c r="L7">
+        <v>556.57067531198504</v>
+      </c>
+      <c r="M7">
+        <v>2.2486234083771699E-2</v>
+      </c>
+      <c r="N7">
+        <v>2.13280487805604E-2</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>17.835397892857099</v>
+      </c>
+      <c r="E8">
+        <v>135334.999210999</v>
+      </c>
+      <c r="F8">
+        <v>135334.999210999</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>135334.999210999</v>
+      </c>
+      <c r="I8">
+        <v>4.6539999999999999</v>
+      </c>
+      <c r="J8">
+        <v>1099.25</v>
+      </c>
+      <c r="K8">
+        <v>5.1158071999999901</v>
+      </c>
+      <c r="L8">
+        <v>692.72591015906698</v>
+      </c>
+      <c r="M8">
+        <v>4.9432292580604498E-2</v>
+      </c>
+      <c r="N8">
+        <v>5.8449652045965098E-2</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>17.589476741138501</v>
+      </c>
+      <c r="E9">
+        <v>98254.817075999803</v>
+      </c>
+      <c r="F9">
+        <v>98254.817075999803</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>98254.817075999803</v>
+      </c>
+      <c r="I9">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J9">
+        <v>1097.1500000000001</v>
+      </c>
+      <c r="K9">
+        <v>5.0903157999999902</v>
+      </c>
+      <c r="L9">
+        <v>500.44370068015098</v>
+      </c>
+      <c r="M9">
+        <v>1.87987945973873E-2</v>
+      </c>
+      <c r="N9">
+        <v>1.7480403184890698E-2</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>17.606867505873101</v>
+      </c>
+      <c r="E10">
+        <v>89935.879220000003</v>
+      </c>
+      <c r="F10">
+        <v>89935.879220000003</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>89935.879220000003</v>
+      </c>
+      <c r="I10">
+        <v>4.6479999999999997</v>
+      </c>
+      <c r="J10">
+        <v>1115.54999999999</v>
+      </c>
+      <c r="K10">
+        <v>5.1850615999999903</v>
+      </c>
+      <c r="L10">
+        <v>466.60044493253599</v>
+      </c>
+      <c r="M10">
+        <v>1.3746597804129099E-2</v>
+      </c>
+      <c r="N10">
+        <v>2.2351743653416599E-2</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>16.551909183789999</v>
+      </c>
+      <c r="E11">
+        <v>141932.621251</v>
+      </c>
+      <c r="F11">
+        <v>141932.621251</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>141932.621251</v>
+      </c>
+      <c r="I11">
+        <v>4.6820000000000004</v>
+      </c>
+      <c r="J11">
+        <v>1014.39999999999</v>
+      </c>
+      <c r="K11">
+        <v>4.7460957999999902</v>
+      </c>
+      <c r="L11">
+        <v>674.00353281267803</v>
+      </c>
+      <c r="M11">
+        <v>3.6901112645864403E-2</v>
+      </c>
+      <c r="N11">
+        <v>5.2505973726511002E-2</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>16.503684502542502</v>
+      </c>
+      <c r="E12">
+        <v>129817.982297</v>
+      </c>
+      <c r="F12">
+        <v>129817.982297</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>129817.982297</v>
+      </c>
+      <c r="I12">
+        <v>4.7119999999999997</v>
+      </c>
+      <c r="J12">
+        <v>921.89999999999895</v>
+      </c>
+      <c r="K12">
+        <v>4.3405727999999897</v>
+      </c>
+      <c r="L12">
+        <v>563.81522189624502</v>
+      </c>
+      <c r="M12">
+        <v>1.53279257938265E-2</v>
+      </c>
+      <c r="N12">
+        <v>2.2899296134710301E-2</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>16.488344777675199</v>
+      </c>
+      <c r="E13">
+        <v>125113.560172999</v>
+      </c>
+      <c r="F13">
+        <v>125113.560172999</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>125113.560172999</v>
+      </c>
+      <c r="I13">
+        <v>4.7519999999999998</v>
+      </c>
+      <c r="J13">
+        <v>828.8</v>
+      </c>
+      <c r="K13">
+        <v>3.9384899999999998</v>
+      </c>
+      <c r="L13">
+        <v>493.05041211694697</v>
+      </c>
+      <c r="M13">
+        <v>4.9432292580604498E-2</v>
+      </c>
+      <c r="N13">
+        <v>5.8449652045965098E-2</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14">
+        <v>16.561569759193201</v>
+      </c>
+      <c r="E14">
+        <v>148623.527019</v>
+      </c>
+      <c r="F14">
+        <v>148623.527019</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>148623.527019</v>
+      </c>
+      <c r="I14">
+        <v>4.694</v>
+      </c>
+      <c r="J14">
+        <v>1001.64999999999</v>
+      </c>
+      <c r="K14">
+        <v>4.6924505999999901</v>
+      </c>
+      <c r="L14">
+        <v>697.81339385375804</v>
+      </c>
+      <c r="M14">
+        <v>7.3200054466724396E-3</v>
+      </c>
+      <c r="N14">
+        <v>7.0026395842432898E-3</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <v>17.6481434336722</v>
+      </c>
+      <c r="E15">
+        <v>145808.96104900001</v>
+      </c>
+      <c r="F15">
+        <v>145808.96104900001</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>145808.96104900001</v>
+      </c>
+      <c r="I15">
+        <v>4.6379999999999999</v>
+      </c>
+      <c r="J15">
+        <v>1129.1499999999901</v>
+      </c>
+      <c r="K15">
+        <v>5.2365951999999902</v>
+      </c>
+      <c r="L15">
+        <v>763.96475779268701</v>
+      </c>
+      <c r="M15">
+        <v>5.18991760909557E-2</v>
+      </c>
+      <c r="N15">
+        <v>8.4807902574539101E-2</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16">
+        <v>17.612464609559499</v>
+      </c>
+      <c r="E16">
+        <v>98383.227308999703</v>
+      </c>
+      <c r="F16">
+        <v>98383.227308999703</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>98383.227308999703</v>
+      </c>
+      <c r="I16">
+        <v>4.6479999999999997</v>
+      </c>
+      <c r="J16">
+        <v>1094.6499999999901</v>
+      </c>
+      <c r="K16">
+        <v>5.0879193999999996</v>
+      </c>
+      <c r="L16">
+        <v>500.86343023825702</v>
+      </c>
+      <c r="M16">
+        <v>1.87987945973873E-2</v>
+      </c>
+      <c r="N16">
+        <v>1.7480403184890698E-2</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17">
+        <v>17.6113443143628</v>
+      </c>
+      <c r="E17">
+        <v>156582.46229899899</v>
+      </c>
+      <c r="F17">
+        <v>156582.46229899899</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>156582.46229899899</v>
+      </c>
+      <c r="I17">
+        <v>4.6379999999999999</v>
+      </c>
+      <c r="J17">
+        <v>1124.75</v>
+      </c>
+      <c r="K17">
+        <v>5.2154541999999902</v>
+      </c>
+      <c r="L17">
+        <v>817.08752189042605</v>
+      </c>
+      <c r="M17">
+        <v>2.8086921200156201E-2</v>
+      </c>
+      <c r="N17">
+        <v>2.6280906051397299E-2</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18">
+        <v>17.627216668754901</v>
+      </c>
+      <c r="E18">
+        <v>90039.822744000005</v>
+      </c>
+      <c r="F18">
+        <v>90039.822744000005</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>90039.822744000005</v>
+      </c>
+      <c r="I18">
+        <v>4.6219999999999999</v>
+      </c>
+      <c r="J18">
+        <v>1143.3999999999901</v>
+      </c>
+      <c r="K18">
+        <v>5.2845987999999897</v>
+      </c>
+      <c r="L18">
+        <v>476.10667947995699</v>
+      </c>
+      <c r="M18">
+        <v>1.3746597804129099E-2</v>
+      </c>
+      <c r="N18">
+        <v>2.2351743653416599E-2</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19">
+        <v>17.575573429423699</v>
+      </c>
+      <c r="E19">
+        <v>103098.313736999</v>
+      </c>
+      <c r="F19">
+        <v>103098.313736999</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>103098.313736999</v>
+      </c>
+      <c r="I19">
+        <v>4.6440000000000001</v>
+      </c>
+      <c r="J19">
+        <v>1127.19999999999</v>
+      </c>
+      <c r="K19">
+        <v>5.2337907999999898</v>
+      </c>
+      <c r="L19">
+        <v>539.90729008301696</v>
+      </c>
+      <c r="M19">
+        <v>2.2486234083771699E-2</v>
+      </c>
+      <c r="N19">
+        <v>2.13280487805604E-2</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20">
+        <v>17.6012753977156</v>
+      </c>
+      <c r="E20">
+        <v>103249.081482999</v>
+      </c>
+      <c r="F20">
+        <v>103249.081482999</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>103249.081482999</v>
+      </c>
+      <c r="I20">
+        <v>4.6319999999999997</v>
+      </c>
+      <c r="J20">
+        <v>1098.25</v>
+      </c>
+      <c r="K20">
+        <v>5.0862649999999903</v>
+      </c>
+      <c r="L20">
+        <v>525.45725874136099</v>
+      </c>
+      <c r="M20">
+        <v>2.2486234083771699E-2</v>
+      </c>
+      <c r="N20">
+        <v>2.13280487805604E-2</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21">
+        <v>17.598587190681201</v>
+      </c>
+      <c r="E21">
+        <v>89893.583369999702</v>
+      </c>
+      <c r="F21">
+        <v>89893.583369999702</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>89893.583369999702</v>
+      </c>
+      <c r="I21">
+        <v>4.6159999999999997</v>
+      </c>
+      <c r="J21">
+        <v>1231.9000000000001</v>
+      </c>
+      <c r="K21">
+        <v>5.6849432000000002</v>
+      </c>
+      <c r="L21">
+        <v>511.345649798274</v>
+      </c>
+      <c r="M21">
+        <v>1.3746597804129099E-2</v>
+      </c>
+      <c r="N21">
+        <v>2.2351743653416599E-2</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22">
+        <v>17.605971844491201</v>
+      </c>
+      <c r="E22">
+        <v>133594.11435599899</v>
+      </c>
+      <c r="F22">
+        <v>133594.11435599899</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>133594.11435599899</v>
+      </c>
+      <c r="I22">
+        <v>4.6479999999999997</v>
+      </c>
+      <c r="J22">
+        <v>1073.44999999999</v>
+      </c>
+      <c r="K22">
+        <v>4.9893955999999902</v>
+      </c>
+      <c r="L22">
+        <v>666.92343048916598</v>
+      </c>
+      <c r="M22">
+        <v>4.9432292580604498E-2</v>
+      </c>
+      <c r="N22">
+        <v>5.8449652045965098E-2</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23">
+        <v>17.610754101069698</v>
+      </c>
+      <c r="E23">
+        <v>158038.90730300001</v>
+      </c>
+      <c r="F23">
+        <v>158038.90730300001</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>158038.90730300001</v>
+      </c>
+      <c r="I23">
+        <v>4.6519999999999904</v>
+      </c>
+      <c r="J23">
+        <v>1076.44999999999</v>
+      </c>
+      <c r="K23">
+        <v>5.0076227999999903</v>
+      </c>
+      <c r="L23">
+        <v>791.81949834819898</v>
+      </c>
+      <c r="M23">
+        <v>7.3200054466724396E-3</v>
+      </c>
+      <c r="N23">
+        <v>7.0026395842432898E-3</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24">
+        <v>17.0449983045267</v>
+      </c>
+      <c r="E24">
+        <v>140825.77599200001</v>
+      </c>
+      <c r="F24">
+        <v>140825.77599200001</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>140825.77599200001</v>
+      </c>
+      <c r="I24">
+        <v>4.6980000000000004</v>
+      </c>
+      <c r="J24">
+        <v>1014.99999999999</v>
+      </c>
+      <c r="K24">
+        <v>4.7541023999999901</v>
+      </c>
+      <c r="L24">
+        <v>669.861052385996</v>
+      </c>
+      <c r="M24">
+        <v>5.18991760909557E-2</v>
+      </c>
+      <c r="N24">
+        <v>8.4807902574539101E-2</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25">
+        <v>16.308552397143099</v>
+      </c>
+      <c r="E25">
+        <v>144999.33936299899</v>
+      </c>
+      <c r="F25">
+        <v>144999.33936299899</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>144999.33936299899</v>
+      </c>
+      <c r="I25">
+        <v>4.7460000000000004</v>
+      </c>
+      <c r="J25">
+        <v>840.4</v>
+      </c>
+      <c r="K25">
+        <v>3.9885653999999899</v>
+      </c>
+      <c r="L25">
+        <v>578.655397401394</v>
+      </c>
+      <c r="M25">
+        <v>2.8086921200156201E-2</v>
+      </c>
+      <c r="N25">
+        <v>2.6280906051397299E-2</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>16.7096417325196</v>
+      </c>
+      <c r="E26">
+        <v>131438.04186799901</v>
+      </c>
+      <c r="F26">
+        <v>131438.04186799901</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>131438.04186799901</v>
+      </c>
+      <c r="I26">
+        <v>4.7059999999999897</v>
+      </c>
+      <c r="J26">
+        <v>924.849999999999</v>
+      </c>
+      <c r="K26">
+        <v>4.3458015999999899</v>
+      </c>
+      <c r="L26">
+        <v>571.52545082844597</v>
+      </c>
+      <c r="M26">
+        <v>1.53279257938265E-2</v>
+      </c>
+      <c r="N26">
+        <v>2.2899296134710301E-2</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27">
+        <v>17.613876010495598</v>
+      </c>
+      <c r="E27">
+        <v>151038.98678999901</v>
+      </c>
+      <c r="F27">
+        <v>151038.98678999901</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>151038.98678999901</v>
+      </c>
+      <c r="I27">
+        <v>4.5960000000000001</v>
+      </c>
+      <c r="J27">
+        <v>1196.19999999999</v>
+      </c>
+      <c r="K27">
+        <v>5.4972791999999897</v>
+      </c>
+      <c r="L27">
+        <v>830.74475063336297</v>
+      </c>
+      <c r="M27">
+        <v>3.6901112645864403E-2</v>
+      </c>
+      <c r="N27">
+        <v>5.2505973726511002E-2</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28">
+        <v>17.629198740601499</v>
+      </c>
+      <c r="E28">
+        <v>98476.704165000207</v>
+      </c>
+      <c r="F28">
+        <v>98476.704165000207</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>98476.704165000207</v>
+      </c>
+      <c r="I28">
+        <v>4.6139999999999999</v>
+      </c>
+      <c r="J28">
+        <v>1233.4000000000001</v>
+      </c>
+      <c r="K28">
+        <v>5.6904085999999996</v>
+      </c>
+      <c r="L28">
+        <v>560.70115309579899</v>
+      </c>
+      <c r="M28">
+        <v>1.87987945973873E-2</v>
+      </c>
+      <c r="N28">
+        <v>1.7480403184890698E-2</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29">
+        <v>17.614068494320001</v>
+      </c>
+      <c r="E29">
+        <v>156606.68298299899</v>
+      </c>
+      <c r="F29">
+        <v>156606.68298299899</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>156606.68298299899</v>
+      </c>
+      <c r="I29">
+        <v>4.6660000000000004</v>
+      </c>
+      <c r="J29">
+        <v>1069.6499999999901</v>
+      </c>
+      <c r="K29">
+        <v>4.9910189999999997</v>
+      </c>
+      <c r="L29">
+        <v>782.03935561375499</v>
+      </c>
+      <c r="M29">
+        <v>2.8086921200156201E-2</v>
+      </c>
+      <c r="N29">
+        <v>2.6280906051397299E-2</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30">
+        <v>17.608266210965802</v>
+      </c>
+      <c r="E30">
+        <v>145479.49543499999</v>
+      </c>
+      <c r="F30">
+        <v>145479.49543499999</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>145479.49543499999</v>
+      </c>
+      <c r="I30">
+        <v>4.6579999999999897</v>
+      </c>
+      <c r="J30">
+        <v>1096.69999999999</v>
+      </c>
+      <c r="K30">
+        <v>5.1084031999999997</v>
+      </c>
+      <c r="L30">
+        <v>743.56865479277803</v>
+      </c>
+      <c r="M30">
+        <v>5.18991760909557E-2</v>
+      </c>
+      <c r="N30">
+        <v>8.4807902574539101E-2</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31">
+        <v>16.611524331543102</v>
+      </c>
+      <c r="E31">
+        <v>92791.974916000006</v>
+      </c>
+      <c r="F31">
+        <v>92791.974916000006</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>92791.974916000006</v>
+      </c>
+      <c r="I31">
+        <v>4.7</v>
+      </c>
+      <c r="J31">
+        <v>952.14999999999895</v>
+      </c>
+      <c r="K31">
+        <v>4.4696150000000001</v>
+      </c>
+      <c r="L31">
+        <v>414.997348681159</v>
+      </c>
+      <c r="M31">
+        <v>1.87987945973873E-2</v>
+      </c>
+      <c r="N31">
+        <v>1.7480403184890698E-2</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32">
+        <v>16.289870733526499</v>
+      </c>
+      <c r="E32">
+        <v>123607.539125999</v>
+      </c>
+      <c r="F32">
+        <v>123607.539125999</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>123607.539125999</v>
+      </c>
+      <c r="I32">
+        <v>4.76</v>
+      </c>
+      <c r="J32">
+        <v>826.14999999999895</v>
+      </c>
+      <c r="K32">
+        <v>3.93235259999999</v>
+      </c>
+      <c r="L32">
+        <v>486.34563429618402</v>
+      </c>
+      <c r="M32">
+        <v>4.9432292580604498E-2</v>
+      </c>
+      <c r="N32">
+        <v>5.8449652045965098E-2</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33">
+        <v>16.311608909819299</v>
+      </c>
+      <c r="E33">
+        <v>95683.897865000297</v>
+      </c>
+      <c r="F33">
+        <v>95683.897865000297</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>95683.897865000297</v>
+      </c>
+      <c r="I33">
+        <v>4.758</v>
+      </c>
+      <c r="J33">
+        <v>804.3</v>
+      </c>
+      <c r="K33">
+        <v>3.82684519999999</v>
+      </c>
+      <c r="L33">
+        <v>366.38817710849798</v>
+      </c>
+      <c r="M33">
+        <v>2.2486234083771699E-2</v>
+      </c>
+      <c r="N33">
+        <v>2.13280487805604E-2</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34">
+        <v>16.3095954377089</v>
+      </c>
+      <c r="E34">
+        <v>146362.30945799901</v>
+      </c>
+      <c r="F34">
+        <v>146362.30945799901</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>146362.30945799901</v>
+      </c>
+      <c r="I34">
+        <v>4.734</v>
+      </c>
+      <c r="J34">
+        <v>874.24999999999898</v>
+      </c>
+      <c r="K34">
+        <v>4.1384759999999901</v>
+      </c>
+      <c r="L34">
+        <v>606.05043459795002</v>
+      </c>
+      <c r="M34">
+        <v>7.3200054466724396E-3</v>
+      </c>
+      <c r="N34">
+        <v>7.0026395842432898E-3</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35">
+        <v>16.314456967230299</v>
+      </c>
+      <c r="E35">
+        <v>139896.468494</v>
+      </c>
+      <c r="F35">
+        <v>139896.468494</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>139896.468494</v>
+      </c>
+      <c r="I35">
+        <v>4.7560000000000002</v>
+      </c>
+      <c r="J35">
+        <v>827.49999999999898</v>
+      </c>
+      <c r="K35">
+        <v>3.9355899999999902</v>
+      </c>
+      <c r="L35">
+        <v>550.884738610829</v>
+      </c>
+      <c r="M35">
+        <v>3.6901112645864403E-2</v>
+      </c>
+      <c r="N35">
+        <v>5.2505973726511002E-2</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36">
+        <v>16.308931137822999</v>
+      </c>
+      <c r="E36">
+        <v>83306.020252000002</v>
+      </c>
+      <c r="F36">
+        <v>83306.020252000002</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>83306.020252000002</v>
+      </c>
+      <c r="I36">
+        <v>4.7480000000000002</v>
+      </c>
+      <c r="J36">
+        <v>881.14999999999895</v>
+      </c>
+      <c r="K36">
+        <v>4.1839653999999999</v>
+      </c>
+      <c r="L36">
+        <v>348.76943401878202</v>
+      </c>
+      <c r="M36">
+        <v>1.3746597804129099E-2</v>
+      </c>
+      <c r="N36">
+        <v>2.2351743653416599E-2</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>16.305875832443402</v>
+      </c>
+      <c r="E37">
+        <v>128262.019298</v>
+      </c>
+      <c r="F37">
+        <v>128262.019298</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>128262.019298</v>
+      </c>
+      <c r="I37">
+        <v>4.7679999999999998</v>
+      </c>
+      <c r="J37">
+        <v>812.65</v>
+      </c>
+      <c r="K37">
+        <v>3.8747402000000002</v>
+      </c>
+      <c r="L37">
+        <v>497.26373921215003</v>
+      </c>
+      <c r="M37">
+        <v>1.53279257938265E-2</v>
+      </c>
+      <c r="N37">
+        <v>2.2899296134710301E-2</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38">
+        <v>16.318854302094898</v>
+      </c>
+      <c r="E38">
+        <v>146445.39850700001</v>
+      </c>
+      <c r="F38">
+        <v>146445.39850700001</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>146445.39850700001</v>
+      </c>
+      <c r="I38">
+        <v>4.7320000000000002</v>
+      </c>
+      <c r="J38">
+        <v>839.19999999999902</v>
+      </c>
+      <c r="K38">
+        <v>3.9702544</v>
+      </c>
+      <c r="L38">
+        <v>581.74620233605594</v>
+      </c>
+      <c r="M38">
+        <v>7.3200054466724396E-3</v>
+      </c>
+      <c r="N38">
+        <v>7.0026395842432898E-3</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39">
+        <v>16.301781363615099</v>
+      </c>
+      <c r="E39">
+        <v>139787.77519300001</v>
+      </c>
+      <c r="F39">
+        <v>139787.77519300001</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>139787.77519300001</v>
+      </c>
+      <c r="I39">
+        <v>4.7640000000000002</v>
+      </c>
+      <c r="J39">
+        <v>816.349999999999</v>
+      </c>
+      <c r="K39">
+        <v>3.8890913999999999</v>
+      </c>
+      <c r="L39">
+        <v>543.95080886875098</v>
+      </c>
+      <c r="M39">
+        <v>3.6901112645864403E-2</v>
+      </c>
+      <c r="N39">
+        <v>5.2505973726511002E-2</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40">
+        <v>16.307062228273999</v>
+      </c>
+      <c r="E40">
+        <v>134728.94813</v>
+      </c>
+      <c r="F40">
+        <v>134728.94813</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>134728.94813</v>
+      </c>
+      <c r="I40">
+        <v>4.7640000000000002</v>
+      </c>
+      <c r="J40">
+        <v>811.099999999999</v>
+      </c>
+      <c r="K40">
+        <v>3.86417239999999</v>
+      </c>
+      <c r="L40">
+        <v>520.90538753767203</v>
+      </c>
+      <c r="M40">
+        <v>5.18991760909557E-2</v>
+      </c>
+      <c r="N40">
+        <v>8.4807902574539101E-2</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41">
+        <v>16.317434272076401</v>
+      </c>
+      <c r="E41">
+        <v>95718.069440000298</v>
+      </c>
+      <c r="F41">
+        <v>95718.069440000298</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>95718.069440000298</v>
+      </c>
+      <c r="I41">
+        <v>4.7379999999999898</v>
+      </c>
+      <c r="J41">
+        <v>893.39999999999895</v>
+      </c>
+      <c r="K41">
+        <v>4.2317955999999999</v>
+      </c>
+      <c r="L41">
+        <v>405.30356292529802</v>
+      </c>
+      <c r="M41">
+        <v>2.2486234083771699E-2</v>
+      </c>
+      <c r="N41">
+        <v>2.13280487805604E-2</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42">
+        <v>16.3396833261551</v>
+      </c>
+      <c r="E42">
+        <v>83463.102430000596</v>
+      </c>
+      <c r="F42">
+        <v>83463.102430000596</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>83463.102430000596</v>
+      </c>
+      <c r="I42">
+        <v>4.7439999999999998</v>
+      </c>
+      <c r="J42">
+        <v>891.64999999999895</v>
+      </c>
+      <c r="K42">
+        <v>4.2285267999999903</v>
+      </c>
+      <c r="L42">
+        <v>353.14937538329502</v>
+      </c>
+      <c r="M42">
+        <v>1.3746597804129099E-2</v>
+      </c>
+      <c r="N42">
+        <v>2.2351743653416599E-2</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43">
+        <v>42</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43">
+        <v>16.322228209014099</v>
+      </c>
+      <c r="E43">
+        <v>123853.06764999899</v>
+      </c>
+      <c r="F43">
+        <v>123853.06764999899</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>123853.06764999899</v>
+      </c>
+      <c r="I43">
+        <v>4.758</v>
+      </c>
+      <c r="J43">
+        <v>851.39999999999895</v>
+      </c>
+      <c r="K43">
+        <v>4.0509917999999896</v>
+      </c>
+      <c r="L43">
+        <v>502.01845545344497</v>
+      </c>
+      <c r="M43">
+        <v>4.9432292580604498E-2</v>
+      </c>
+      <c r="N43">
+        <v>5.8449652045965098E-2</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44">
+        <v>16.310822399928401</v>
+      </c>
+      <c r="E44">
+        <v>91112.253926000398</v>
+      </c>
+      <c r="F44">
+        <v>91112.253926000398</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>91112.253926000398</v>
+      </c>
+      <c r="I44">
+        <v>4.7140000000000004</v>
+      </c>
+      <c r="J44">
+        <v>922.89999999999895</v>
+      </c>
+      <c r="K44">
+        <v>4.3505941999999997</v>
+      </c>
+      <c r="L44">
+        <v>396.63296757633299</v>
+      </c>
+      <c r="M44">
+        <v>1.87987945973873E-2</v>
+      </c>
+      <c r="N44">
+        <v>1.7480403184890698E-2</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45">
+        <v>44</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>16.328930638062499</v>
+      </c>
+      <c r="E45">
+        <v>128443.368399</v>
+      </c>
+      <c r="F45">
+        <v>128443.368399</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>128443.368399</v>
+      </c>
+      <c r="I45">
+        <v>4.726</v>
+      </c>
+      <c r="J45">
+        <v>915.19999999999902</v>
+      </c>
+      <c r="K45">
+        <v>4.3256117999999901</v>
+      </c>
+      <c r="L45">
+        <v>555.91183953818097</v>
+      </c>
+      <c r="M45">
+        <v>1.53279257938265E-2</v>
+      </c>
+      <c r="N45">
+        <v>2.2899296134710301E-2</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46">
+        <v>16.308559349342001</v>
+      </c>
+      <c r="E46">
+        <v>144999.40117500001</v>
+      </c>
+      <c r="F46">
+        <v>144999.40117500001</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>144999.40117500001</v>
+      </c>
+      <c r="I46">
+        <v>4.718</v>
+      </c>
+      <c r="J46">
+        <v>895.599999999999</v>
+      </c>
+      <c r="K46">
+        <v>4.2254197999999903</v>
+      </c>
+      <c r="L46">
+        <v>613.022091384531</v>
+      </c>
+      <c r="M46">
+        <v>2.8086921200156201E-2</v>
+      </c>
+      <c r="N46">
+        <v>2.6280906051397299E-2</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47">
+        <v>16.306875686537701</v>
+      </c>
+      <c r="E47">
+        <v>91090.207584999895</v>
+      </c>
+      <c r="F47">
+        <v>91090.207584999895</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>91090.207584999895</v>
+      </c>
+      <c r="I47">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="J47">
+        <v>953.74999999999898</v>
+      </c>
+      <c r="K47">
+        <v>4.5112957999999903</v>
+      </c>
+      <c r="L47">
+        <v>411.18437952713703</v>
+      </c>
+      <c r="M47">
+        <v>1.87987945973873E-2</v>
+      </c>
+      <c r="N47">
+        <v>1.7480403184890698E-2</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48">
+        <v>16.304200747775202</v>
+      </c>
+      <c r="E48">
+        <v>128248.84308200001</v>
+      </c>
+      <c r="F48">
+        <v>128248.84308200001</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>128248.84308200001</v>
+      </c>
+      <c r="I48">
+        <v>4.7359999999999998</v>
+      </c>
+      <c r="J48">
+        <v>873.4</v>
+      </c>
+      <c r="K48">
+        <v>4.1361703999999904</v>
+      </c>
+      <c r="L48">
+        <v>530.75454829795603</v>
+      </c>
+      <c r="M48">
+        <v>1.53279257938265E-2</v>
+      </c>
+      <c r="N48">
+        <v>2.2899296134710301E-2</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49">
+        <v>48</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49">
+        <v>16.3133480591253</v>
+      </c>
+      <c r="E49">
+        <v>139886.95960699901</v>
+      </c>
+      <c r="F49">
+        <v>139886.95960699901</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>139886.95960699901</v>
+      </c>
+      <c r="I49">
+        <v>4.7319999999999904</v>
+      </c>
+      <c r="J49">
+        <v>856.349999999999</v>
+      </c>
+      <c r="K49">
+        <v>4.0515663999999996</v>
+      </c>
+      <c r="L49">
+        <v>567.07564557405999</v>
+      </c>
+      <c r="M49">
+        <v>3.6901112645864403E-2</v>
+      </c>
+      <c r="N49">
+        <v>5.2505973726511002E-2</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50">
+        <v>49</v>
+      </c>
+      <c r="C50" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50">
+        <v>16.342709812515</v>
+      </c>
+      <c r="E50">
+        <v>135023.46847099901</v>
+      </c>
+      <c r="F50">
+        <v>135023.46847099901</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>135023.46847099901</v>
+      </c>
+      <c r="I50">
+        <v>4.7560000000000002</v>
+      </c>
+      <c r="J50">
+        <v>844.599999999999</v>
+      </c>
+      <c r="K50">
+        <v>4.0168707999999897</v>
+      </c>
+      <c r="L50">
+        <v>542.67678706035099</v>
+      </c>
+      <c r="M50">
+        <v>5.18991760909557E-2</v>
+      </c>
+      <c r="N50">
+        <v>8.4807902574539101E-2</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51">
+        <v>16.300179510628599</v>
+      </c>
+      <c r="E51">
+        <v>144924.89602899901</v>
+      </c>
+      <c r="F51">
+        <v>144924.89602899901</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>144924.89602899901</v>
+      </c>
+      <c r="I51">
+        <v>4.76</v>
+      </c>
+      <c r="J51">
+        <v>833.55</v>
+      </c>
+      <c r="K51">
+        <v>3.9676979999999902</v>
+      </c>
+      <c r="L51">
+        <v>575.334750548854</v>
+      </c>
+      <c r="M51">
+        <v>2.8086921200156201E-2</v>
+      </c>
+      <c r="N51">
+        <v>2.6280906051397299E-2</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>